--- a/planering/kemi-omrade1/kemi-1-kahoot.xlsx
+++ b/planering/kemi-omrade1/kemi-1-kahoot.xlsx
@@ -1880,17 +1880,17 @@
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
+          <t>Hörlurar</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>Vantar av ull</t>
+        </is>
+      </c>
+      <c r="F9" s="14" t="inlineStr">
+        <is>
           <t>Solglasögon</t>
-        </is>
-      </c>
-      <c r="E9" s="14" t="inlineStr">
-        <is>
-          <t>Vantar av ull</t>
-        </is>
-      </c>
-      <c r="F9" s="14" t="inlineStr">
-        <is>
-          <t>Hörlurar</t>
         </is>
       </c>
       <c r="G9" s="14" t="n">
@@ -1932,22 +1932,22 @@
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
+          <t>90 000</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="E10" s="14" t="inlineStr">
+        <is>
+          <t>1177</t>
+        </is>
+      </c>
+      <c r="F10" s="14" t="inlineStr">
+        <is>
           <t>020 20 20</t>
-        </is>
-      </c>
-      <c r="D10" s="14" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="E10" s="14" t="inlineStr">
-        <is>
-          <t>90 000</t>
-        </is>
-      </c>
-      <c r="F10" s="14" t="inlineStr">
-        <is>
-          <t>1177</t>
         </is>
       </c>
       <c r="G10" s="14" t="n">
@@ -1989,22 +1989,22 @@
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
+          <t>Vem som har tillverkat ämnet</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
           <t>Hur gammalt ämnet är</t>
         </is>
       </c>
-      <c r="D11" s="21" t="inlineStr">
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t>Vilken fara ett ämne har</t>
+        </is>
+      </c>
+      <c r="F11" s="14" t="inlineStr">
         <is>
           <t>Vad ämnet kostar</t>
-        </is>
-      </c>
-      <c r="E11" s="14" t="inlineStr">
-        <is>
-          <t>Vilken fara ett ämne har</t>
-        </is>
-      </c>
-      <c r="F11" s="14" t="inlineStr">
-        <is>
-          <t>Vem som har tillverkat ämnet</t>
         </is>
       </c>
       <c r="G11" s="14" t="n">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
+          <t>Mätcylinder</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>Termometer</t>
+        </is>
+      </c>
+      <c r="E12" s="14" t="inlineStr">
+        <is>
           <t>Klocka</t>
-        </is>
-      </c>
-      <c r="D12" s="14" t="inlineStr">
-        <is>
-          <t>Mätcylinder</t>
-        </is>
-      </c>
-      <c r="E12" s="14" t="inlineStr">
-        <is>
-          <t>Termometer</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
@@ -2108,17 +2108,17 @@
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
+          <t>En slutsats</t>
+        </is>
+      </c>
+      <c r="E13" s="14" t="inlineStr">
+        <is>
+          <t>Ett säkert svar</t>
+        </is>
+      </c>
+      <c r="F13" s="14" t="inlineStr">
+        <is>
           <t>En tabell med mätvärden</t>
-        </is>
-      </c>
-      <c r="E13" s="14" t="inlineStr">
-        <is>
-          <t>En slutsats</t>
-        </is>
-      </c>
-      <c r="F13" s="14" t="inlineStr">
-        <is>
-          <t>Ett säkert svar</t>
         </is>
       </c>
       <c r="G13" s="14" t="n">
@@ -2160,22 +2160,22 @@
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
+          <t>Medelvärde</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>Oberoende variabel</t>
+        </is>
+      </c>
+      <c r="E14" s="14" t="inlineStr">
+        <is>
           <t>Beroende variabel</t>
         </is>
       </c>
-      <c r="D14" s="14" t="inlineStr">
-        <is>
-          <t>Oberoende variabel</t>
-        </is>
-      </c>
-      <c r="E14" s="14" t="inlineStr">
+      <c r="F14" s="14" t="inlineStr">
         <is>
           <t>Felkälla</t>
-        </is>
-      </c>
-      <c r="F14" s="14" t="inlineStr">
-        <is>
-          <t>Medelvärde</t>
         </is>
       </c>
       <c r="G14" s="14" t="n">
@@ -2217,22 +2217,22 @@
       </c>
       <c r="C15" s="14" t="inlineStr">
         <is>
+          <t>Hypotes</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="inlineStr">
+        <is>
           <t>Oberoende variabel</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="E15" s="14" t="inlineStr">
+        <is>
+          <t>Beroende variabel</t>
+        </is>
+      </c>
+      <c r="F15" s="14" t="inlineStr">
         <is>
           <t>Modell</t>
-        </is>
-      </c>
-      <c r="E15" s="14" t="inlineStr">
-        <is>
-          <t>Beroende variabel</t>
-        </is>
-      </c>
-      <c r="F15" s="14" t="inlineStr">
-        <is>
-          <t>Hypotes</t>
         </is>
       </c>
       <c r="G15" s="14" t="n">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
+          <t>Då behöver man inte mäta</t>
+        </is>
+      </c>
+      <c r="E16" s="14" t="inlineStr">
+        <is>
           <t>Det går snabbare</t>
-        </is>
-      </c>
-      <c r="E16" s="14" t="inlineStr">
-        <is>
-          <t>Då behöver man inte mäta</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
@@ -2336,17 +2336,17 @@
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
+          <t>29 s</t>
+        </is>
+      </c>
+      <c r="E17" s="14" t="inlineStr">
+        <is>
+          <t>93 s</t>
+        </is>
+      </c>
+      <c r="F17" s="14" t="inlineStr">
+        <is>
           <t>33 s</t>
-        </is>
-      </c>
-      <c r="E17" s="14" t="inlineStr">
-        <is>
-          <t>29 s</t>
-        </is>
-      </c>
-      <c r="F17" s="14" t="inlineStr">
-        <is>
-          <t>93 s</t>
         </is>
       </c>
       <c r="G17" s="14" t="n">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="C19" s="14" t="inlineStr">
         <is>
+          <t>Ett försök som lyckats</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="inlineStr">
+        <is>
           <t>En sorts diagram</t>
-        </is>
-      </c>
-      <c r="D19" s="14" t="inlineStr">
-        <is>
-          <t>Ett försök som lyckats</t>
         </is>
       </c>
       <c r="E19" s="14" t="inlineStr">
@@ -2502,12 +2502,12 @@
       </c>
       <c r="C20" s="14" t="inlineStr">
         <is>
+          <t>För att få fler siffror att skriva ner</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
           <t>För att slippa en slutsats</t>
-        </is>
-      </c>
-      <c r="D20" s="14" t="inlineStr">
-        <is>
-          <t>För att få fler siffror att skriva ner</t>
         </is>
       </c>
       <c r="E20" s="14" t="inlineStr">
@@ -2616,17 +2616,17 @@
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
+          <t>Dalton</t>
+        </is>
+      </c>
+      <c r="D22" s="14" t="inlineStr">
+        <is>
+          <t>Boyle</t>
+        </is>
+      </c>
+      <c r="E22" s="14" t="inlineStr">
+        <is>
           <t>Empedokles</t>
-        </is>
-      </c>
-      <c r="D22" s="14" t="inlineStr">
-        <is>
-          <t>Boyle</t>
-        </is>
-      </c>
-      <c r="E22" s="14" t="inlineStr">
-        <is>
-          <t>Dalton</t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">
@@ -2673,22 +2673,22 @@
       </c>
       <c r="C23" s="14" t="inlineStr">
         <is>
+          <t>Att atomer är odelbara</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t>Att guld kan tillverkas</t>
+        </is>
+      </c>
+      <c r="E23" s="14" t="inlineStr">
+        <is>
+          <t>Att massan är lika stor före och efter en reaktion</t>
+        </is>
+      </c>
+      <c r="F23" s="14" t="inlineStr">
+        <is>
           <t>Att allt består av fyra element</t>
-        </is>
-      </c>
-      <c r="D23" s="14" t="inlineStr">
-        <is>
-          <t>Att guld kan tillverkas</t>
-        </is>
-      </c>
-      <c r="E23" s="14" t="inlineStr">
-        <is>
-          <t>Att massan är lika stor före och efter en reaktion</t>
-        </is>
-      </c>
-      <c r="F23" s="14" t="inlineStr">
-        <is>
-          <t>Att atomer är odelbara</t>
         </is>
       </c>
       <c r="G23" s="14" t="n">
@@ -2730,17 +2730,17 @@
       </c>
       <c r="C24" s="14" t="inlineStr">
         <is>
+          <t>Boyle</t>
+        </is>
+      </c>
+      <c r="D24" s="14" t="inlineStr">
+        <is>
+          <t>Lavoisier</t>
+        </is>
+      </c>
+      <c r="E24" s="14" t="inlineStr">
+        <is>
           <t>Aristoteles</t>
-        </is>
-      </c>
-      <c r="D24" s="14" t="inlineStr">
-        <is>
-          <t>Lavoisier</t>
-        </is>
-      </c>
-      <c r="E24" s="14" t="inlineStr">
-        <is>
-          <t>Boyle</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="D25" s="14" t="inlineStr">
         <is>
+          <t>Atomer och molekyler</t>
+        </is>
+      </c>
+      <c r="E25" s="14" t="inlineStr">
+        <is>
           <t>Hundra grundämnen</t>
-        </is>
-      </c>
-      <c r="E25" s="14" t="inlineStr">
-        <is>
-          <t>Atomer och molekyler</t>
         </is>
       </c>
       <c r="F25" s="14" t="inlineStr">
@@ -2854,12 +2854,12 @@
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
+          <t>Tabletten blev tyngre</t>
+        </is>
+      </c>
+      <c r="F26" s="14" t="inlineStr">
+        <is>
           <t>Den löser sig fortare i kallare vatten</t>
-        </is>
-      </c>
-      <c r="F26" s="14" t="inlineStr">
-        <is>
-          <t>Tabletten blev tyngre</t>
         </is>
       </c>
       <c r="G26" s="14" t="n">
@@ -2901,12 +2901,12 @@
       </c>
       <c r="C27" s="14" t="inlineStr">
         <is>
+          <t>Att tro på allt man läser</t>
+        </is>
+      </c>
+      <c r="D27" s="14" t="inlineStr">
+        <is>
           <t>Att aldrig använda internet</t>
-        </is>
-      </c>
-      <c r="D27" s="14" t="inlineStr">
-        <is>
-          <t>Att tro på allt man läser</t>
         </is>
       </c>
       <c r="E27" s="14" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="C28" s="14" t="inlineStr">
         <is>
+          <t>Hur stor är bilden?</t>
+        </is>
+      </c>
+      <c r="D28" s="14" t="inlineStr">
+        <is>
+          <t>Vilken färg har förpackningen?</t>
+        </is>
+      </c>
+      <c r="E28" s="14" t="inlineStr">
+        <is>
           <t>Vem är längst?</t>
-        </is>
-      </c>
-      <c r="D28" s="14" t="inlineStr">
-        <is>
-          <t>Vilken färg har förpackningen?</t>
-        </is>
-      </c>
-      <c r="E28" s="14" t="inlineStr">
-        <is>
-          <t>Hur stor är bilden?</t>
         </is>
       </c>
       <c r="F28" s="14" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="D29" s="16" t="inlineStr">
         <is>
+          <t>Inget ämne</t>
+        </is>
+      </c>
+      <c r="E29" s="16" t="inlineStr">
+        <is>
           <t>Något som är kemikaliefritt</t>
-        </is>
-      </c>
-      <c r="E29" s="16" t="inlineStr">
-        <is>
-          <t>Inget ämne</t>
         </is>
       </c>
       <c r="F29" s="16" t="inlineStr">
@@ -3072,22 +3072,22 @@
       </c>
       <c r="C30" s="16" t="inlineStr">
         <is>
+          <t>Ja, naturligt är alltid ofarligt</t>
+        </is>
+      </c>
+      <c r="D30" s="16" t="inlineStr">
+        <is>
+          <t>Nej, vissa naturliga ämnen är giftiga</t>
+        </is>
+      </c>
+      <c r="E30" s="16" t="inlineStr">
+        <is>
           <t>Ja, men bara i skogen</t>
         </is>
       </c>
-      <c r="D30" s="16" t="inlineStr">
-        <is>
-          <t>Nej, vissa naturliga ämnen är giftiga</t>
-        </is>
-      </c>
-      <c r="E30" s="16" t="inlineStr">
+      <c r="F30" s="16" t="inlineStr">
         <is>
           <t>Bara om det är gratis</t>
-        </is>
-      </c>
-      <c r="F30" s="16" t="inlineStr">
-        <is>
-          <t>Ja, naturligt är alltid ofarligt</t>
         </is>
       </c>
       <c r="G30" s="14" t="n">
